--- a/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Average Price of Gold and Silver in Domestic and Foreign Markets.xlsx
+++ b/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Average Price of Gold and Silver in Domestic and Foreign Markets.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="70">
   <si>
     <t>Year</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Cents per troy oz.</t>
   </si>
   <si>
+    <t xml:space="preserve">2025-26   </t>
+  </si>
+  <si>
     <t xml:space="preserve">2024-25   </t>
   </si>
   <si>
@@ -214,12 +217,11 @@
     <t>Average Price of Gold and Silver in Domestic and Foreign Markets</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes     : 1. The data source for this Table for the period till 1999-2000 are  Bombay Bullion Association and  Press Trust of India. 
-                    For the period 2000-01 onwards, the data sources are (i) Business Standard/ Business Line and Economic 
-                   Times, Mumbai/IBJA Website for gold and silver price in Mumbai and LBMA for gold price in London and (ii) Thomson 
-                    Reuters for silver price in New York.
-               2. Data provided in this Table for the period 1979-80 to 1999-2000 and 2000-01 to 2020-21 may not be strictly comparable
-                   due to different sources of information.</t>
+    <t xml:space="preserve">Note    : Data provided in this Table for the period 1983-84 to 1999-2000 and 2000-01 to 2025-26 may not be strictly comparable due to different sources of 
+              information.
+Source : The data source for this Table for the period till 1999-2000 is Bombay Bullion Association and Press Trust of India. For the period 2000-01 onwards, the 
+             data sources are (i) Business Standard/ Business Line and Economic Times, Mumbai/IBJA Website for gold and silver price in Mumbai and LBMA for 
+             gold price in London and (ii) Thomson Reuters for silver price in New York</t>
   </si>
 </sst>
 </file>
@@ -390,7 +392,7 @@
     <xf numFmtId="49" fontId="3" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="1" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="1" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -405,16 +407,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:L66"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
-    <col min="2" max="11" width="15.4582386666667" customWidth="1"/>
+    <col min="2" max="10" width="15.4582386666667" customWidth="1"/>
+    <col min="11" max="11" width="42256e-6" customWidth="1"/>
+    <col min="12" max="12" width="15.385988" customWidth="1"/>
+    <col min="13" max="13" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
     <row r="2" s="1" customFormat="1" ht="20.7987" customHeight="1">
       <c r="B2" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -425,6 +430,7 @@
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
       <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
     <row r="4" s="1" customFormat="1" ht="23.9985" customHeight="1">
@@ -524,28 +530,28 @@
         <v>12</v>
       </c>
       <c r="C8" s="8">
-        <v>75841.874613</v>
+        <v>118420.9</v>
       </c>
       <c r="D8" s="8">
-        <v>2584.53</v>
+        <v>3937.86</v>
       </c>
       <c r="E8" s="8">
-        <v>70315.41</v>
+        <v>112381.86</v>
       </c>
       <c r="F8" s="8">
-        <v>5526.464613</v>
+        <v>6039.04</v>
       </c>
       <c r="G8" s="8">
-        <v>89130.530889</v>
+        <v>162672.25</v>
       </c>
       <c r="H8" s="8">
-        <v>3039.215719</v>
+        <v>5308.67300075</v>
       </c>
       <c r="I8" s="8">
-        <v>82685.101934</v>
+        <v>152150.08635475</v>
       </c>
       <c r="J8" s="8">
-        <v>11700.171068</v>
+        <v>10522.16364525</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -553,28 +559,28 @@
         <v>13</v>
       </c>
       <c r="C9" s="9">
-        <v>60623.950833</v>
+        <v>75841.874613</v>
       </c>
       <c r="D9" s="9">
-        <v>1989</v>
+        <v>2584.53</v>
       </c>
       <c r="E9" s="9">
-        <v>52684.42</v>
+        <v>70315.41</v>
       </c>
       <c r="F9" s="9">
-        <v>7939.530833</v>
+        <v>5526.464613</v>
       </c>
       <c r="G9" s="9">
-        <v>72242.818333</v>
+        <v>89130.530889</v>
       </c>
       <c r="H9" s="9">
-        <v>2360.380778</v>
+        <v>3039.215719</v>
       </c>
       <c r="I9" s="9">
-        <v>62821.013097</v>
+        <v>82685.101934</v>
       </c>
       <c r="J9" s="9">
-        <v>9421.805236</v>
+        <v>6445.428955</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -582,28 +588,28 @@
         <v>14</v>
       </c>
       <c r="C10" s="8">
-        <v>52730.77</v>
+        <v>60623.950833</v>
       </c>
       <c r="D10" s="8">
-        <v>1804.82</v>
+        <v>1989</v>
       </c>
       <c r="E10" s="8">
-        <v>46605.74</v>
+        <v>52684.42</v>
       </c>
       <c r="F10" s="8">
-        <v>6125.03</v>
+        <v>7939.530833</v>
       </c>
       <c r="G10" s="8">
-        <v>61990.56</v>
+        <v>72242.818333</v>
       </c>
       <c r="H10" s="8">
-        <v>2142.751899</v>
+        <v>2360.380778</v>
       </c>
       <c r="I10" s="8">
-        <v>55347.952279</v>
+        <v>62821.013097</v>
       </c>
       <c r="J10" s="8">
-        <v>6642.61</v>
+        <v>9421.805236</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -611,28 +617,28 @@
         <v>15</v>
       </c>
       <c r="C11" s="9">
-        <v>47999.245</v>
+        <v>52730.77</v>
       </c>
       <c r="D11" s="9">
-        <v>1818.425833</v>
+        <v>1804.82</v>
       </c>
       <c r="E11" s="9">
-        <v>43582.250833</v>
+        <v>46605.74</v>
       </c>
       <c r="F11" s="9">
-        <v>4416.995833</v>
+        <v>6125.03</v>
       </c>
       <c r="G11" s="9">
-        <v>65425.645833</v>
+        <v>61990.56</v>
       </c>
       <c r="H11" s="9">
-        <v>2457.399037</v>
+        <v>2142.751899</v>
       </c>
       <c r="I11" s="9">
-        <v>58847.677905</v>
+        <v>55347.952279</v>
       </c>
       <c r="J11" s="9">
-        <v>6577.967928</v>
+        <v>6642.61</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -640,28 +646,28 @@
         <v>16</v>
       </c>
       <c r="C12" s="8">
-        <v>48723.224167</v>
+        <v>47999.245</v>
       </c>
       <c r="D12" s="8">
-        <v>1824.083333</v>
+        <v>1818.425833</v>
       </c>
       <c r="E12" s="8">
-        <v>43541.0025</v>
+        <v>43582.250833</v>
       </c>
       <c r="F12" s="8">
-        <v>5182.2225</v>
+        <v>4416.995833</v>
       </c>
       <c r="G12" s="8">
-        <v>59283.2625</v>
+        <v>65425.645833</v>
       </c>
       <c r="H12" s="8">
-        <v>2289.460062</v>
+        <v>2457.399037</v>
       </c>
       <c r="I12" s="8">
-        <v>54499.055552</v>
+        <v>58847.677905</v>
       </c>
       <c r="J12" s="8">
-        <v>4784.206948</v>
+        <v>6577.967928</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -669,28 +675,28 @@
         <v>17</v>
       </c>
       <c r="C13" s="9">
-        <v>37017.909243</v>
+        <v>48723.224167</v>
       </c>
       <c r="D13" s="9">
-        <v>1462.145747</v>
+        <v>1824.083333</v>
       </c>
       <c r="E13" s="9">
-        <v>33346.533315</v>
+        <v>43541.0025</v>
       </c>
       <c r="F13" s="9">
-        <v>3670.542594</v>
+        <v>5182.2225</v>
       </c>
       <c r="G13" s="9">
-        <v>42514.304169</v>
+        <v>59283.2625</v>
       </c>
       <c r="H13" s="9">
-        <v>1652.781869</v>
+        <v>2289.460062</v>
       </c>
       <c r="I13" s="9">
-        <v>37687.890327</v>
+        <v>54499.055552</v>
       </c>
       <c r="J13" s="9">
-        <v>4826.413843</v>
+        <v>4784.206948</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -698,28 +704,28 @@
         <v>18</v>
       </c>
       <c r="C14" s="8">
-        <v>31193.405495</v>
+        <v>37017.909243</v>
       </c>
       <c r="D14" s="8">
-        <v>1263.163454</v>
+        <v>1462.145747</v>
       </c>
       <c r="E14" s="8">
-        <v>28380.356575</v>
+        <v>33346.533315</v>
       </c>
       <c r="F14" s="8">
-        <v>2813.04892</v>
+        <v>3670.542594</v>
       </c>
       <c r="G14" s="8">
-        <v>38404.234498</v>
+        <v>42514.304169</v>
       </c>
       <c r="H14" s="8">
-        <v>1538.552886</v>
+        <v>1652.781869</v>
       </c>
       <c r="I14" s="8">
-        <v>34540.19603</v>
+        <v>37687.890327</v>
       </c>
       <c r="J14" s="8">
-        <v>3864.038468</v>
+        <v>4826.413843</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -727,28 +733,28 @@
         <v>19</v>
       </c>
       <c r="C15" s="9">
-        <v>29300.076667</v>
+        <v>31193.405495</v>
       </c>
       <c r="D15" s="9">
-        <v>1285.2825</v>
+        <v>1263.163454</v>
       </c>
       <c r="E15" s="9">
-        <v>26618.553333</v>
+        <v>28380.356575</v>
       </c>
       <c r="F15" s="9">
-        <v>2681.523333</v>
+        <v>2813.04892</v>
       </c>
       <c r="G15" s="9">
-        <v>39072.184167</v>
+        <v>38404.234498</v>
       </c>
       <c r="H15" s="9">
-        <v>1687.158176</v>
+        <v>1538.552886</v>
       </c>
       <c r="I15" s="9">
-        <v>34961.96865</v>
+        <v>34540.19603</v>
       </c>
       <c r="J15" s="9">
-        <v>4110.215517</v>
+        <v>3864.038468</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -756,28 +762,28 @@
         <v>20</v>
       </c>
       <c r="C16" s="8">
-        <v>29665.284167</v>
+        <v>29300.076667</v>
       </c>
       <c r="D16" s="8">
-        <v>1258.029167</v>
+        <v>1285.2825</v>
       </c>
       <c r="E16" s="8">
-        <v>27116.419167</v>
+        <v>26618.553333</v>
       </c>
       <c r="F16" s="8">
-        <v>2548.865</v>
+        <v>2681.523333</v>
       </c>
       <c r="G16" s="8">
-        <v>42748.314167</v>
+        <v>39072.184167</v>
       </c>
       <c r="H16" s="8">
-        <v>1779.075</v>
+        <v>1687.158176</v>
       </c>
       <c r="I16" s="8">
-        <v>38360.040006</v>
+        <v>34961.96865</v>
       </c>
       <c r="J16" s="8">
-        <v>4388.274161</v>
+        <v>4110.215517</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -785,28 +791,28 @@
         <v>21</v>
       </c>
       <c r="C17" s="9">
-        <v>26534.261667</v>
+        <v>29665.284167</v>
       </c>
       <c r="D17" s="9">
-        <v>1147.426667</v>
+        <v>1258.029167</v>
       </c>
       <c r="E17" s="9">
-        <v>24231.531667</v>
+        <v>27116.419167</v>
       </c>
       <c r="F17" s="9">
-        <v>2302.73</v>
+        <v>2548.865</v>
       </c>
       <c r="G17" s="9">
-        <v>36318.103333</v>
+        <v>42748.314167</v>
       </c>
       <c r="H17" s="9">
-        <v>1526.025</v>
+        <v>1779.075</v>
       </c>
       <c r="I17" s="9">
-        <v>32091.839965</v>
+        <v>38360.040006</v>
       </c>
       <c r="J17" s="9">
-        <v>4226.263368</v>
+        <v>4388.274161</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -814,28 +820,28 @@
         <v>22</v>
       </c>
       <c r="C18" s="8">
-        <v>27414.554167</v>
+        <v>26534.261667</v>
       </c>
       <c r="D18" s="8">
-        <v>1247.400833</v>
+        <v>1147.426667</v>
       </c>
       <c r="E18" s="8">
-        <v>24520.423333</v>
+        <v>24231.531667</v>
       </c>
       <c r="F18" s="8">
-        <v>2894.130833</v>
+        <v>2302.73</v>
       </c>
       <c r="G18" s="8">
-        <v>40558.48</v>
+        <v>36318.103333</v>
       </c>
       <c r="H18" s="8">
-        <v>1814.041667</v>
+        <v>1526.025</v>
       </c>
       <c r="I18" s="8">
-        <v>35611.177123</v>
+        <v>32091.839965</v>
       </c>
       <c r="J18" s="8">
-        <v>4947.302877</v>
+        <v>4226.263368</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -843,28 +849,28 @@
         <v>23</v>
       </c>
       <c r="C19" s="9">
-        <v>29190.3925</v>
+        <v>27414.554167</v>
       </c>
       <c r="D19" s="9">
-        <v>1326.681667</v>
+        <v>1247.400833</v>
       </c>
       <c r="E19" s="9">
-        <v>25739.354167</v>
+        <v>24520.423333</v>
       </c>
       <c r="F19" s="9">
-        <v>3451.038333</v>
+        <v>2894.130833</v>
       </c>
       <c r="G19" s="9">
-        <v>46636.795833</v>
+        <v>40558.48</v>
       </c>
       <c r="H19" s="9">
-        <v>2145.414516</v>
+        <v>1814.041667</v>
       </c>
       <c r="I19" s="9">
-        <v>41643.209509</v>
+        <v>35611.177123</v>
       </c>
       <c r="J19" s="9">
-        <v>4993.586324</v>
+        <v>4947.302877</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -872,28 +878,28 @@
         <v>24</v>
       </c>
       <c r="C20" s="8">
-        <v>30163.9325</v>
+        <v>29190.3925</v>
       </c>
       <c r="D20" s="8">
-        <v>1653.506667</v>
+        <v>1326.681667</v>
       </c>
       <c r="E20" s="8">
-        <v>28919.0425</v>
+        <v>25739.354167</v>
       </c>
       <c r="F20" s="8">
-        <v>1244.89</v>
+        <v>3451.038333</v>
       </c>
       <c r="G20" s="8">
-        <v>57602.304167</v>
+        <v>46636.795833</v>
       </c>
       <c r="H20" s="8">
-        <v>3050.714583</v>
+        <v>2145.414516</v>
       </c>
       <c r="I20" s="8">
-        <v>53329.110447</v>
+        <v>41643.209509</v>
       </c>
       <c r="J20" s="8">
-        <v>4273.19372</v>
+        <v>4993.586324</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -901,28 +907,28 @@
         <v>25</v>
       </c>
       <c r="C21" s="9">
-        <v>25722.423333</v>
+        <v>30163.9325</v>
       </c>
       <c r="D21" s="9">
-        <v>1644.865833</v>
+        <v>1653.506667</v>
       </c>
       <c r="E21" s="9">
-        <v>25394.0325</v>
+        <v>28919.0425</v>
       </c>
       <c r="F21" s="9">
-        <v>328.390833</v>
+        <v>1244.89</v>
       </c>
       <c r="G21" s="9">
-        <v>57315.8675</v>
+        <v>57602.304167</v>
       </c>
       <c r="H21" s="9">
-        <v>3545.6425</v>
+        <v>3050.714583</v>
       </c>
       <c r="I21" s="9">
-        <v>54320.685331</v>
+        <v>53329.110447</v>
       </c>
       <c r="J21" s="9">
-        <v>2995.182169</v>
+        <v>4273.19372</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -930,28 +936,28 @@
         <v>26</v>
       </c>
       <c r="C22" s="8">
-        <v>19227.084167</v>
+        <v>25722.423333</v>
       </c>
       <c r="D22" s="8">
-        <v>1293.533333</v>
+        <v>1644.865833</v>
       </c>
       <c r="E22" s="8">
-        <v>18937.483333</v>
+        <v>25394.0325</v>
       </c>
       <c r="F22" s="8">
-        <v>289.600833</v>
+        <v>328.390833</v>
       </c>
       <c r="G22" s="8">
-        <v>37289.539167</v>
+        <v>57315.8675</v>
       </c>
       <c r="H22" s="8">
-        <v>2391.155</v>
+        <v>3545.6425</v>
       </c>
       <c r="I22" s="8">
-        <v>35050.9325</v>
+        <v>54320.685331</v>
       </c>
       <c r="J22" s="8">
-        <v>2238.606667</v>
+        <v>2995.182169</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -959,28 +965,28 @@
         <v>27</v>
       </c>
       <c r="C23" s="9">
-        <v>15756.0925</v>
+        <v>19227.084167</v>
       </c>
       <c r="D23" s="9">
-        <v>1023.028333</v>
+        <v>1293.533333</v>
       </c>
       <c r="E23" s="9">
-        <v>15569.875</v>
+        <v>18937.483333</v>
       </c>
       <c r="F23" s="9">
-        <v>186.2175</v>
+        <v>289.600833</v>
       </c>
       <c r="G23" s="9">
-        <v>25320.6925</v>
+        <v>37289.539167</v>
       </c>
       <c r="H23" s="9">
-        <v>1576.298333</v>
+        <v>2391.155</v>
       </c>
       <c r="I23" s="9">
-        <v>23980.038333</v>
+        <v>35050.9325</v>
       </c>
       <c r="J23" s="9">
-        <v>1340.654167</v>
+        <v>2238.606667</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -988,28 +994,28 @@
         <v>28</v>
       </c>
       <c r="C24" s="8">
-        <v>12889.7425</v>
+        <v>15756.0925</v>
       </c>
       <c r="D24" s="8">
-        <v>867.189167</v>
+        <v>1023.028333</v>
       </c>
       <c r="E24" s="8">
-        <v>12816.806667</v>
+        <v>15569.875</v>
       </c>
       <c r="F24" s="8">
-        <v>72.935833</v>
+        <v>186.2175</v>
       </c>
       <c r="G24" s="8">
-        <v>21247.571667</v>
+        <v>25320.6925</v>
       </c>
       <c r="H24" s="8">
-        <v>1374.975833</v>
+        <v>1576.298333</v>
       </c>
       <c r="I24" s="8">
-        <v>20059.438333</v>
+        <v>23980.038333</v>
       </c>
       <c r="J24" s="8">
-        <v>1188.133333</v>
+        <v>1340.654167</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1017,28 +1023,28 @@
         <v>29</v>
       </c>
       <c r="C25" s="9">
-        <v>9995.616667</v>
+        <v>12889.7425</v>
       </c>
       <c r="D25" s="9">
-        <v>765.784167</v>
+        <v>867.189167</v>
       </c>
       <c r="E25" s="9">
-        <v>9897.118333</v>
+        <v>12816.806667</v>
       </c>
       <c r="F25" s="9">
-        <v>98.498333</v>
+        <v>72.935833</v>
       </c>
       <c r="G25" s="9">
-        <v>19427.45</v>
+        <v>21247.571667</v>
       </c>
       <c r="H25" s="9">
-        <v>1448.958333</v>
+        <v>1374.975833</v>
       </c>
       <c r="I25" s="9">
-        <v>18738.231667</v>
+        <v>20059.438333</v>
       </c>
       <c r="J25" s="9">
-        <v>689.218333</v>
+        <v>1188.133333</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1046,28 +1052,28 @@
         <v>30</v>
       </c>
       <c r="C26" s="8">
-        <v>9240.324167</v>
+        <v>9995.616667</v>
       </c>
       <c r="D26" s="8">
-        <v>628.408333</v>
+        <v>765.784167</v>
       </c>
       <c r="E26" s="8">
-        <v>9137.79</v>
+        <v>9897.118333</v>
       </c>
       <c r="F26" s="8">
-        <v>102.534167</v>
+        <v>98.498333</v>
       </c>
       <c r="G26" s="8">
-        <v>19056.571667</v>
+        <v>19427.45</v>
       </c>
       <c r="H26" s="8">
-        <v>1247.741667</v>
+        <v>1448.958333</v>
       </c>
       <c r="I26" s="8">
-        <v>18133.956667</v>
+        <v>18738.231667</v>
       </c>
       <c r="J26" s="8">
-        <v>922.615</v>
+        <v>689.218333</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1075,28 +1081,28 @@
         <v>31</v>
       </c>
       <c r="C27" s="9">
-        <v>6900.56</v>
+        <v>9240.324167</v>
       </c>
       <c r="D27" s="9">
-        <v>476.5825</v>
+        <v>628.408333</v>
       </c>
       <c r="E27" s="9">
-        <v>6790.255</v>
+        <v>9137.79</v>
       </c>
       <c r="F27" s="9">
-        <v>110.305</v>
+        <v>102.534167</v>
       </c>
       <c r="G27" s="9">
-        <v>11828.813333</v>
+        <v>19056.571667</v>
       </c>
       <c r="H27" s="9">
-        <v>801.173333</v>
+        <v>1247.741667</v>
       </c>
       <c r="I27" s="9">
-        <v>11417.365833</v>
+        <v>18133.956667</v>
       </c>
       <c r="J27" s="9">
-        <v>411.4475</v>
+        <v>922.615</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1104,28 +1110,28 @@
         <v>32</v>
       </c>
       <c r="C28" s="8">
-        <v>6145.384167</v>
+        <v>6900.56</v>
       </c>
       <c r="D28" s="8">
-        <v>413.948333</v>
+        <v>476.5825</v>
       </c>
       <c r="E28" s="8">
-        <v>5976.14</v>
+        <v>6790.255</v>
       </c>
       <c r="F28" s="8">
-        <v>169.244167</v>
+        <v>110.305</v>
       </c>
       <c r="G28" s="8">
-        <v>10680.819167</v>
+        <v>11828.813333</v>
       </c>
       <c r="H28" s="8">
-        <v>676.166667</v>
+        <v>801.173333</v>
       </c>
       <c r="I28" s="8">
-        <v>9766.579167</v>
+        <v>11417.365833</v>
       </c>
       <c r="J28" s="8">
-        <v>914.24</v>
+        <v>411.4475</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1133,28 +1139,28 @@
         <v>33</v>
       </c>
       <c r="C29" s="9">
-        <v>5718.945833</v>
+        <v>6145.384167</v>
       </c>
       <c r="D29" s="9">
-        <v>377.645</v>
+        <v>413.948333</v>
       </c>
       <c r="E29" s="9">
-        <v>5573.534167</v>
+        <v>5976.14</v>
       </c>
       <c r="F29" s="9">
-        <v>145.411667</v>
+        <v>169.244167</v>
       </c>
       <c r="G29" s="9">
-        <v>8721.895833</v>
+        <v>10680.819167</v>
       </c>
       <c r="H29" s="9">
-        <v>541.55</v>
+        <v>676.166667</v>
       </c>
       <c r="I29" s="9">
-        <v>7982.494167</v>
+        <v>9766.579167</v>
       </c>
       <c r="J29" s="9">
-        <v>739.401667</v>
+        <v>914.24</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1162,28 +1168,28 @@
         <v>34</v>
       </c>
       <c r="C30" s="8">
-        <v>5332.3625</v>
+        <v>5718.945833</v>
       </c>
       <c r="D30" s="8">
-        <v>325.4875</v>
+        <v>377.645</v>
       </c>
       <c r="E30" s="8">
-        <v>5062.110833</v>
+        <v>5573.534167</v>
       </c>
       <c r="F30" s="8">
-        <v>270.251667</v>
+        <v>145.411667</v>
       </c>
       <c r="G30" s="8">
-        <v>7990.528333</v>
+        <v>8721.895833</v>
       </c>
       <c r="H30" s="8">
-        <v>467.233333</v>
+        <v>541.55</v>
       </c>
       <c r="I30" s="8">
-        <v>7268.461667</v>
+        <v>7982.494167</v>
       </c>
       <c r="J30" s="8">
-        <v>722.066667</v>
+        <v>739.401667</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1191,28 +1197,28 @@
         <v>35</v>
       </c>
       <c r="C31" s="9">
-        <v>4579.119167</v>
+        <v>5332.3625</v>
       </c>
       <c r="D31" s="9">
-        <v>277.735</v>
+        <v>325.4875</v>
       </c>
       <c r="E31" s="9">
-        <v>4260.234167</v>
+        <v>5062.110833</v>
       </c>
       <c r="F31" s="9">
-        <v>318.885</v>
+        <v>270.251667</v>
       </c>
       <c r="G31" s="9">
-        <v>7447.1925</v>
+        <v>7990.528333</v>
       </c>
       <c r="H31" s="9">
-        <v>437.341667</v>
+        <v>467.233333</v>
       </c>
       <c r="I31" s="9">
-        <v>6708.705</v>
+        <v>7268.461667</v>
       </c>
       <c r="J31" s="9">
-        <v>738.4875</v>
+        <v>722.066667</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1220,28 +1226,28 @@
         <v>36</v>
       </c>
       <c r="C32" s="8">
-        <v>4473.598333</v>
+        <v>4579.119167</v>
       </c>
       <c r="D32" s="8">
-        <v>272.120833</v>
+        <v>277.735</v>
       </c>
       <c r="E32" s="8">
-        <v>4007.786667</v>
+        <v>4260.234167</v>
       </c>
       <c r="F32" s="8">
-        <v>465.539167</v>
+        <v>318.885</v>
       </c>
       <c r="G32" s="8">
-        <v>7868.39</v>
+        <v>7447.1925</v>
       </c>
       <c r="H32" s="8">
-        <v>483.591667</v>
+        <v>437.341667</v>
       </c>
       <c r="I32" s="8">
-        <v>7110.183333</v>
+        <v>6708.705</v>
       </c>
       <c r="J32" s="8">
-        <v>758.206667</v>
+        <v>738.4875</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1249,28 +1255,28 @@
         <v>37</v>
       </c>
       <c r="C33" s="9">
-        <v>4393.555833</v>
+        <v>4473.598333</v>
       </c>
       <c r="D33" s="9">
-        <v>279.646667</v>
+        <v>272.120833</v>
       </c>
       <c r="E33" s="9">
-        <v>3896.661667</v>
+        <v>4007.786667</v>
       </c>
       <c r="F33" s="9">
-        <v>496.895</v>
+        <v>465.539167</v>
       </c>
       <c r="G33" s="9">
-        <v>8066.9425</v>
+        <v>7868.39</v>
       </c>
       <c r="H33" s="9">
-        <v>522.683333</v>
+        <v>483.591667</v>
       </c>
       <c r="I33" s="9">
-        <v>7286.511667</v>
+        <v>7110.183333</v>
       </c>
       <c r="J33" s="9">
-        <v>780.430833</v>
+        <v>758.206667</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1278,28 +1284,28 @@
         <v>38</v>
       </c>
       <c r="C34" s="8">
-        <v>4268.166667</v>
+        <v>4393.555833</v>
       </c>
       <c r="D34" s="8">
-        <v>292.319167</v>
+        <v>279.646667</v>
       </c>
       <c r="E34" s="8">
-        <v>3952.25</v>
+        <v>3896.661667</v>
       </c>
       <c r="F34" s="8">
-        <v>316.083333</v>
+        <v>496.895</v>
       </c>
       <c r="G34" s="8">
-        <v>7855.333333</v>
+        <v>8066.9425</v>
       </c>
       <c r="H34" s="8">
-        <v>529.79225</v>
+        <v>522.683333</v>
       </c>
       <c r="I34" s="8">
-        <v>7143.916667</v>
+        <v>7286.511667</v>
       </c>
       <c r="J34" s="8">
-        <v>711.416667</v>
+        <v>780.430833</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1307,28 +1313,28 @@
         <v>39</v>
       </c>
       <c r="C35" s="9">
-        <v>4347.066667</v>
+        <v>4268.166667</v>
       </c>
       <c r="D35" s="9">
-        <v>316.939167</v>
+        <v>292.319167</v>
       </c>
       <c r="E35" s="9">
-        <v>3775.919167</v>
+        <v>3952.25</v>
       </c>
       <c r="F35" s="9">
-        <v>571.1375</v>
+        <v>316.083333</v>
       </c>
       <c r="G35" s="9">
-        <v>7352.274167</v>
+        <v>7855.333333</v>
       </c>
       <c r="H35" s="9">
-        <v>519.996667</v>
+        <v>529.79225</v>
       </c>
       <c r="I35" s="9">
-        <v>6153.959167</v>
+        <v>7143.916667</v>
       </c>
       <c r="J35" s="9">
-        <v>1198.315</v>
+        <v>711.416667</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1336,28 +1342,28 @@
         <v>40</v>
       </c>
       <c r="C36" s="8">
-        <v>5070.711667</v>
+        <v>4347.066667</v>
       </c>
       <c r="D36" s="8">
-        <v>375.523333</v>
+        <v>316.939167</v>
       </c>
       <c r="E36" s="8">
-        <v>4285.604167</v>
+        <v>3775.919167</v>
       </c>
       <c r="F36" s="8">
-        <v>786.774167</v>
+        <v>571.1375</v>
       </c>
       <c r="G36" s="8">
-        <v>7165.07</v>
+        <v>7352.274167</v>
       </c>
       <c r="H36" s="8">
-        <v>505.325833</v>
+        <v>519.996667</v>
       </c>
       <c r="I36" s="8">
-        <v>5762.649167</v>
+        <v>6153.959167</v>
       </c>
       <c r="J36" s="8">
-        <v>1402.420833</v>
+        <v>1198.315</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1365,28 +1371,28 @@
         <v>41</v>
       </c>
       <c r="C37" s="9">
-        <v>4957.604167</v>
+        <v>5070.711667</v>
       </c>
       <c r="D37" s="9">
-        <v>389.364167</v>
+        <v>375.523333</v>
       </c>
       <c r="E37" s="9">
-        <v>4188.575833</v>
+        <v>4285.604167</v>
       </c>
       <c r="F37" s="9">
-        <v>769.028333</v>
+        <v>786.774167</v>
       </c>
       <c r="G37" s="9">
-        <v>7220.5025</v>
+        <v>7165.07</v>
       </c>
       <c r="H37" s="9">
-        <v>540.0475</v>
+        <v>505.325833</v>
       </c>
       <c r="I37" s="9">
-        <v>5809.36</v>
+        <v>5762.649167</v>
       </c>
       <c r="J37" s="9">
-        <v>1411.1425</v>
+        <v>1402.420833</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1394,28 +1400,28 @@
         <v>42</v>
       </c>
       <c r="C38" s="8">
-        <v>4667.24</v>
+        <v>4957.604167</v>
       </c>
       <c r="D38" s="8">
-        <v>382.788333</v>
+        <v>389.364167</v>
       </c>
       <c r="E38" s="8">
-        <v>3864.151667</v>
+        <v>4188.575833</v>
       </c>
       <c r="F38" s="8">
-        <v>803.088333</v>
+        <v>769.028333</v>
       </c>
       <c r="G38" s="8">
-        <v>6692.3075</v>
+        <v>7220.5025</v>
       </c>
       <c r="H38" s="8">
-        <v>513.851667</v>
+        <v>540.0475</v>
       </c>
       <c r="I38" s="8">
-        <v>5187.330833</v>
+        <v>5809.36</v>
       </c>
       <c r="J38" s="8">
-        <v>1504.976667</v>
+        <v>1411.1425</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1423,28 +1429,28 @@
         <v>43</v>
       </c>
       <c r="C39" s="9">
-        <v>4531.865833</v>
+        <v>4667.24</v>
       </c>
       <c r="D39" s="9">
-        <v>373.423333</v>
+        <v>382.788333</v>
       </c>
       <c r="E39" s="9">
-        <v>3766.2825</v>
+        <v>3864.151667</v>
       </c>
       <c r="F39" s="9">
-        <v>765.583333</v>
+        <v>803.088333</v>
       </c>
       <c r="G39" s="9">
-        <v>6348.121667</v>
+        <v>6692.3075</v>
       </c>
       <c r="H39" s="9">
-        <v>470.535</v>
+        <v>513.851667</v>
       </c>
       <c r="I39" s="9">
-        <v>4741.0925</v>
+        <v>5187.330833</v>
       </c>
       <c r="J39" s="9">
-        <v>1607.029167</v>
+        <v>1504.976667</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1452,28 +1458,28 @@
         <v>44</v>
       </c>
       <c r="C40" s="8">
-        <v>4103.660833</v>
+        <v>4531.865833</v>
       </c>
       <c r="D40" s="8">
-        <v>338.354167</v>
+        <v>373.423333</v>
       </c>
       <c r="E40" s="8">
-        <v>3332.949167</v>
+        <v>3766.2825</v>
       </c>
       <c r="F40" s="8">
-        <v>770.711667</v>
+        <v>765.583333</v>
       </c>
       <c r="G40" s="8">
-        <v>7078.390833</v>
+        <v>6348.121667</v>
       </c>
       <c r="H40" s="8">
-        <v>381.97</v>
+        <v>470.535</v>
       </c>
       <c r="I40" s="8">
-        <v>3749.869167</v>
+        <v>4741.0925</v>
       </c>
       <c r="J40" s="8">
-        <v>3328.521667</v>
+        <v>1607.029167</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1481,28 +1487,28 @@
         <v>45</v>
       </c>
       <c r="C41" s="9">
-        <v>4297.628333</v>
+        <v>4103.660833</v>
       </c>
       <c r="D41" s="9">
-        <v>357.3975</v>
+        <v>338.354167</v>
       </c>
       <c r="E41" s="9">
-        <v>2841.074167</v>
+        <v>3332.949167</v>
       </c>
       <c r="F41" s="9">
-        <v>1456.554167</v>
+        <v>770.711667</v>
       </c>
       <c r="G41" s="9">
-        <v>7332.413333</v>
+        <v>7078.390833</v>
       </c>
       <c r="H41" s="9">
-        <v>409.335</v>
+        <v>381.97</v>
       </c>
       <c r="I41" s="9">
-        <v>3269.890833</v>
+        <v>3749.869167</v>
       </c>
       <c r="J41" s="9">
-        <v>4062.5225</v>
+        <v>3328.521667</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1510,28 +1516,28 @@
         <v>46</v>
       </c>
       <c r="C42" s="8">
-        <v>3451.524167</v>
+        <v>4297.628333</v>
       </c>
       <c r="D42" s="8">
-        <v>374.6475</v>
+        <v>357.3975</v>
       </c>
       <c r="E42" s="8">
-        <v>2164.264167</v>
+        <v>2841.074167</v>
       </c>
       <c r="F42" s="8">
-        <v>1287.26</v>
+        <v>1456.554167</v>
       </c>
       <c r="G42" s="8">
-        <v>6760.7875</v>
+        <v>7332.413333</v>
       </c>
       <c r="H42" s="8">
-        <v>449.861667</v>
+        <v>409.335</v>
       </c>
       <c r="I42" s="8">
-        <v>2579.205</v>
+        <v>3269.890833</v>
       </c>
       <c r="J42" s="8">
-        <v>4181.5825</v>
+        <v>4062.5225</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1539,28 +1545,28 @@
         <v>47</v>
       </c>
       <c r="C43" s="9">
-        <v>3229.33</v>
+        <v>3451.524167</v>
       </c>
       <c r="D43" s="9">
-        <v>384.79</v>
+        <v>374.6475</v>
       </c>
       <c r="E43" s="9">
-        <v>2063.01</v>
+        <v>2164.264167</v>
       </c>
       <c r="F43" s="9">
-        <v>1166.32</v>
+        <v>1287.26</v>
       </c>
       <c r="G43" s="9">
-        <v>6841.91</v>
+        <v>6760.7875</v>
       </c>
       <c r="H43" s="9">
-        <v>531.61</v>
+        <v>449.861667</v>
       </c>
       <c r="I43" s="9">
-        <v>2846.31</v>
+        <v>2579.205</v>
       </c>
       <c r="J43" s="9">
-        <v>3995.6</v>
+        <v>4181.5825</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1568,28 +1574,28 @@
         <v>48</v>
       </c>
       <c r="C44" s="8">
-        <v>3175.22</v>
+        <v>3229.33</v>
       </c>
       <c r="D44" s="8">
-        <v>422.01</v>
+        <v>384.79</v>
       </c>
       <c r="E44" s="8">
-        <v>1960.38</v>
+        <v>2063.01</v>
       </c>
       <c r="F44" s="8">
-        <v>1214.84</v>
+        <v>1166.32</v>
       </c>
       <c r="G44" s="8">
-        <v>6366.76</v>
+        <v>6841.91</v>
       </c>
       <c r="H44" s="8">
-        <v>639.65</v>
+        <v>531.61</v>
       </c>
       <c r="I44" s="8">
-        <v>2971.52</v>
+        <v>2846.31</v>
       </c>
       <c r="J44" s="8">
-        <v>3395.24</v>
+        <v>3995.6</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1597,28 +1603,28 @@
         <v>49</v>
       </c>
       <c r="C45" s="9">
-        <v>3082.43</v>
+        <v>3175.22</v>
       </c>
       <c r="D45" s="9">
-        <v>458.84</v>
+        <v>422.01</v>
       </c>
       <c r="E45" s="9">
-        <v>1912.54</v>
+        <v>1960.38</v>
       </c>
       <c r="F45" s="9">
-        <v>1169.89</v>
+        <v>1214.84</v>
       </c>
       <c r="G45" s="9">
-        <v>5538.83</v>
+        <v>6366.76</v>
       </c>
       <c r="H45" s="9">
-        <v>721.49</v>
+        <v>639.65</v>
       </c>
       <c r="I45" s="9">
-        <v>3016.7</v>
+        <v>2971.52</v>
       </c>
       <c r="J45" s="9">
-        <v>2522.13</v>
+        <v>3395.24</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1626,28 +1632,28 @@
         <v>50</v>
       </c>
       <c r="C46" s="8">
-        <v>2323.49</v>
+        <v>3082.43</v>
       </c>
       <c r="D46" s="8">
-        <v>383.33</v>
+        <v>458.84</v>
       </c>
       <c r="E46" s="8">
-        <v>1577.02</v>
+        <v>1912.54</v>
       </c>
       <c r="F46" s="8">
-        <v>746.46</v>
+        <v>1169.89</v>
       </c>
       <c r="G46" s="8">
-        <v>4247.1</v>
+        <v>5538.83</v>
       </c>
       <c r="H46" s="8">
-        <v>539.87</v>
+        <v>721.49</v>
       </c>
       <c r="I46" s="8">
-        <v>2220.03</v>
+        <v>3016.7</v>
       </c>
       <c r="J46" s="8">
-        <v>2027.07</v>
+        <v>2522.13</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1655,28 +1661,28 @@
         <v>51</v>
       </c>
       <c r="C47" s="9">
-        <v>2125.47</v>
+        <v>2323.49</v>
       </c>
       <c r="D47" s="9">
-        <v>327.75</v>
+        <v>383.33</v>
       </c>
       <c r="E47" s="9">
-        <v>1289.76</v>
+        <v>1577.02</v>
       </c>
       <c r="F47" s="9">
-        <v>835.71</v>
+        <v>746.46</v>
       </c>
       <c r="G47" s="9">
-        <v>3918.38</v>
+        <v>4247.1</v>
       </c>
       <c r="H47" s="9">
-        <v>609</v>
+        <v>539.87</v>
       </c>
       <c r="I47" s="9">
-        <v>2396.35</v>
+        <v>2220.03</v>
       </c>
       <c r="J47" s="9">
-        <v>1522.03</v>
+        <v>2027.07</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1684,28 +1690,28 @@
         <v>52</v>
       </c>
       <c r="C48" s="8">
-        <v>1983.92</v>
+        <v>2125.47</v>
       </c>
       <c r="D48" s="8">
-        <v>340.01</v>
+        <v>327.75</v>
       </c>
       <c r="E48" s="8">
-        <v>1293.78</v>
+        <v>1289.76</v>
       </c>
       <c r="F48" s="8">
-        <v>690.13</v>
+        <v>835.71</v>
       </c>
       <c r="G48" s="8">
-        <v>3593.59</v>
+        <v>3918.38</v>
       </c>
       <c r="H48" s="8">
-        <v>740.98</v>
+        <v>609</v>
       </c>
       <c r="I48" s="8">
-        <v>2810.19</v>
+        <v>2396.35</v>
       </c>
       <c r="J48" s="8">
-        <v>783.4</v>
+        <v>1522.03</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1713,28 +1719,28 @@
         <v>53</v>
       </c>
       <c r="C49" s="9">
-        <v>1858.47</v>
+        <v>1983.92</v>
       </c>
       <c r="D49" s="9">
-        <v>404.15</v>
+        <v>340.01</v>
       </c>
       <c r="E49" s="9">
-        <v>1342.06</v>
+        <v>1293.78</v>
       </c>
       <c r="F49" s="9">
-        <v>516.41</v>
+        <v>690.13</v>
       </c>
       <c r="G49" s="9">
-        <v>3505.8</v>
+        <v>3593.59</v>
       </c>
       <c r="H49" s="9">
-        <v>1060.64</v>
+        <v>740.98</v>
       </c>
       <c r="I49" s="9">
-        <v>3516.66</v>
+        <v>2810.19</v>
       </c>
       <c r="J49" s="9">
-        <v>-10.86</v>
+        <v>783.4</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1742,28 +1748,28 @@
         <v>54</v>
       </c>
       <c r="C50" s="8">
-        <v>1722.54</v>
+        <v>1858.47</v>
       </c>
       <c r="D50" s="8">
-        <v>401.43</v>
+        <v>404.15</v>
       </c>
       <c r="E50" s="8">
-        <v>1250.38</v>
+        <v>1342.06</v>
       </c>
       <c r="F50" s="8">
-        <v>472.16</v>
+        <v>516.41</v>
       </c>
       <c r="G50" s="8">
-        <v>2798.34</v>
+        <v>3505.8</v>
       </c>
       <c r="H50" s="8">
-        <v>906.49</v>
+        <v>1060.64</v>
       </c>
       <c r="I50" s="8">
-        <v>2829.46</v>
+        <v>3516.66</v>
       </c>
       <c r="J50" s="8">
-        <v>-31.12</v>
+        <v>-10.86</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1771,28 +1777,28 @@
         <v>55</v>
       </c>
       <c r="C51" s="9">
-        <v>1719.17</v>
+        <v>1722.54</v>
       </c>
       <c r="D51" s="9">
-        <v>420.95</v>
+        <v>401.43</v>
       </c>
       <c r="E51" s="9">
-        <v>1209.94</v>
+        <v>1250.38</v>
       </c>
       <c r="F51" s="9">
-        <v>509.23</v>
+        <v>472.16</v>
       </c>
       <c r="G51" s="9">
-        <v>2636.06</v>
+        <v>2798.34</v>
       </c>
       <c r="H51" s="9">
-        <v>914.52</v>
+        <v>906.49</v>
       </c>
       <c r="I51" s="9">
-        <v>2617.36</v>
+        <v>2829.46</v>
       </c>
       <c r="J51" s="9">
-        <v>18.7</v>
+        <v>-31.12</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1800,28 +1806,28 @@
         <v>56</v>
       </c>
       <c r="C52" s="8">
-        <v>1522.44</v>
+        <v>1719.17</v>
       </c>
       <c r="D52" s="8">
-        <v>584.92</v>
+        <v>420.95</v>
       </c>
       <c r="E52" s="8">
-        <v>1484.67</v>
+        <v>1209.94</v>
       </c>
       <c r="F52" s="8">
-        <v>37.76</v>
+        <v>509.23</v>
       </c>
       <c r="G52" s="8">
-        <v>2617.61</v>
+        <v>2636.06</v>
       </c>
       <c r="H52" s="8">
-        <v>1585.14</v>
+        <v>914.52</v>
       </c>
       <c r="I52" s="8">
-        <v>4020.3</v>
+        <v>2617.36</v>
       </c>
       <c r="J52" s="8">
-        <v>-1402.69</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1829,28 +1835,28 @@
         <v>57</v>
       </c>
       <c r="C53" s="9">
-        <v>1158.75</v>
+        <v>1522.44</v>
       </c>
       <c r="D53" s="9">
-        <v>405.38</v>
+        <v>584.92</v>
       </c>
       <c r="E53" s="9">
-        <v>1052.88</v>
+        <v>1484.67</v>
       </c>
       <c r="F53" s="9">
-        <v>105.87</v>
+        <v>37.76</v>
       </c>
       <c r="G53" s="9">
-        <v>2301.3</v>
+        <v>2617.61</v>
       </c>
       <c r="H53" s="9">
-        <v>1748.88</v>
+        <v>1585.14</v>
       </c>
       <c r="I53" s="9">
-        <v>4532</v>
+        <v>4020.3</v>
       </c>
       <c r="J53" s="9">
-        <v>-2230.7</v>
+        <v>-1402.69</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1858,28 +1864,28 @@
         <v>58</v>
       </c>
       <c r="C54" s="8">
-        <v>791.22</v>
+        <v>1158.75</v>
       </c>
       <c r="D54" s="8">
-        <v>208.29</v>
+        <v>405.38</v>
       </c>
       <c r="E54" s="8">
-        <v>550.12</v>
+        <v>1052.88</v>
       </c>
       <c r="F54" s="8">
-        <v>241.1</v>
+        <v>105.87</v>
       </c>
       <c r="G54" s="8">
-        <v>1500.94</v>
+        <v>2301.3</v>
       </c>
       <c r="H54" s="8">
-        <v>589.92</v>
+        <v>1748.88</v>
       </c>
       <c r="I54" s="8">
-        <v>1559.13</v>
+        <v>4532</v>
       </c>
       <c r="J54" s="8">
-        <v>-58.19</v>
+        <v>-2230.7</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1887,28 +1893,28 @@
         <v>59</v>
       </c>
       <c r="C55" s="9">
-        <v>637.93</v>
+        <v>791.22</v>
       </c>
       <c r="D55" s="9">
-        <v>157.56</v>
+        <v>208.29</v>
       </c>
       <c r="E55" s="9">
-        <v>433.83</v>
+        <v>550.12</v>
       </c>
       <c r="F55" s="9">
-        <v>204.09</v>
+        <v>241.1</v>
       </c>
       <c r="G55" s="9">
-        <v>1240.54</v>
+        <v>1500.94</v>
       </c>
       <c r="H55" s="9">
-        <v>473.46</v>
+        <v>589.92</v>
       </c>
       <c r="I55" s="9">
-        <v>1305.77</v>
+        <v>1559.13</v>
       </c>
       <c r="J55" s="9">
-        <v>-65.24</v>
+        <v>-58.19</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1916,28 +1922,28 @@
         <v>60</v>
       </c>
       <c r="C56" s="8">
-        <v>549.82</v>
+        <v>637.93</v>
       </c>
       <c r="D56" s="8">
-        <v>126.64</v>
+        <v>157.56</v>
       </c>
       <c r="E56" s="8">
-        <v>369.59</v>
+        <v>433.83</v>
       </c>
       <c r="F56" s="8">
-        <v>180.22</v>
+        <v>204.09</v>
       </c>
       <c r="G56" s="8">
-        <v>1247.89</v>
+        <v>1240.54</v>
       </c>
       <c r="H56" s="8">
-        <v>447.58</v>
+        <v>473.46</v>
       </c>
       <c r="I56" s="8">
-        <v>1291.78</v>
+        <v>1305.77</v>
       </c>
       <c r="J56" s="8">
-        <v>-43.9</v>
+        <v>-65.24</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1945,28 +1951,28 @@
         <v>61</v>
       </c>
       <c r="C57" s="9">
-        <v>545.21</v>
+        <v>549.82</v>
       </c>
       <c r="D57" s="9">
-        <v>149.49</v>
+        <v>126.64</v>
       </c>
       <c r="E57" s="9">
-        <v>415.79</v>
+        <v>369.59</v>
       </c>
       <c r="F57" s="9">
-        <v>129.42</v>
+        <v>180.22</v>
       </c>
       <c r="G57" s="9">
-        <v>1171.64</v>
+        <v>1247.89</v>
       </c>
       <c r="H57" s="9">
-        <v>437.36</v>
+        <v>447.58</v>
       </c>
       <c r="I57" s="9">
-        <v>1220.06</v>
+        <v>1291.78</v>
       </c>
       <c r="J57" s="9">
-        <v>-48.42</v>
+        <v>-43.9</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -1974,28 +1980,28 @@
         <v>62</v>
       </c>
       <c r="C58" s="8">
-        <v>519.19</v>
+        <v>545.21</v>
       </c>
       <c r="D58" s="8">
-        <v>166.37</v>
+        <v>149.49</v>
       </c>
       <c r="E58" s="8">
-        <v>424.73</v>
+        <v>415.79</v>
       </c>
       <c r="F58" s="8">
-        <v>94.46</v>
+        <v>129.42</v>
       </c>
       <c r="G58" s="8">
-        <v>1122.4</v>
+        <v>1171.64</v>
       </c>
       <c r="H58" s="8">
-        <v>458.83</v>
+        <v>437.36</v>
       </c>
       <c r="I58" s="8">
-        <v>1170.86</v>
+        <v>1220.06</v>
       </c>
       <c r="J58" s="8">
-        <v>-48.46</v>
+        <v>-48.42</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -2003,28 +2009,28 @@
         <v>63</v>
       </c>
       <c r="C59" s="9">
-        <v>369.33</v>
+        <v>519.19</v>
       </c>
       <c r="D59" s="9">
-        <v>115.77</v>
+        <v>166.37</v>
       </c>
       <c r="E59" s="9">
-        <v>291.17</v>
+        <v>424.73</v>
       </c>
       <c r="F59" s="9">
-        <v>78.16</v>
+        <v>94.46</v>
       </c>
       <c r="G59" s="9">
-        <v>799.01</v>
+        <v>1122.4</v>
       </c>
       <c r="H59" s="9">
-        <v>320.08</v>
+        <v>458.83</v>
       </c>
       <c r="I59" s="9">
-        <v>809.59</v>
+        <v>1170.86</v>
       </c>
       <c r="J59" s="9">
-        <v>-10.58</v>
+        <v>-48.46</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -2032,28 +2038,28 @@
         <v>64</v>
       </c>
       <c r="C60" s="8">
-        <v>242.57</v>
+        <v>369.33</v>
       </c>
       <c r="D60" s="8">
-        <v>64.86</v>
+        <v>115.77</v>
       </c>
       <c r="E60" s="8">
-        <v>160.31</v>
+        <v>291.17</v>
       </c>
       <c r="F60" s="8">
-        <v>82.26</v>
+        <v>78.16</v>
       </c>
       <c r="G60" s="8">
-        <v>554.24</v>
+        <v>799.01</v>
       </c>
       <c r="H60" s="8">
-        <v>185.54</v>
+        <v>320.08</v>
       </c>
       <c r="I60" s="8">
-        <v>458.89</v>
+        <v>809.59</v>
       </c>
       <c r="J60" s="8">
-        <v>95.35</v>
+        <v>-10.58</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -2061,79 +2067,109 @@
         <v>65</v>
       </c>
       <c r="C61" s="9">
+        <v>242.57</v>
+      </c>
+      <c r="D61" s="9">
+        <v>64.86</v>
+      </c>
+      <c r="E61" s="9">
+        <v>160.31</v>
+      </c>
+      <c r="F61" s="9">
+        <v>82.26</v>
+      </c>
+      <c r="G61" s="9">
+        <v>554.24</v>
+      </c>
+      <c r="H61" s="9">
+        <v>185.54</v>
+      </c>
+      <c r="I61" s="9">
+        <v>458.89</v>
+      </c>
+      <c r="J61" s="9">
+        <v>95.35</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" ht="19.7321" customHeight="1">
+      <c r="B62" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" s="8">
         <v>200.16</v>
       </c>
-      <c r="D61" s="9">
+      <c r="D62" s="8">
         <v>43.01</v>
       </c>
-      <c r="E61" s="9">
+      <c r="E62" s="8">
         <v>103.33</v>
       </c>
-      <c r="F61" s="9">
+      <c r="F62" s="8">
         <v>96.83</v>
       </c>
-      <c r="G61" s="9">
+      <c r="G62" s="8">
         <v>561.35</v>
       </c>
-      <c r="H61" s="9">
+      <c r="H62" s="8">
         <v>151.3</v>
       </c>
-      <c r="I61" s="9">
+      <c r="I62" s="8">
         <v>363.51</v>
       </c>
-      <c r="J61" s="9">
+      <c r="J62" s="8">
         <v>197.84</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" ht="19.7321" customHeight="1">
-      <c r="B62" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C62" s="11">
+    <row r="63" s="1" customFormat="1" ht="19.7321" customHeight="1">
+      <c r="B63" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C63" s="11">
         <v>184.96</v>
       </c>
-      <c r="D62" s="11">
+      <c r="D63" s="11">
         <v>36.81</v>
       </c>
-      <c r="E62" s="11">
+      <c r="E63" s="11">
         <v>89.44</v>
       </c>
-      <c r="F62" s="11">
+      <c r="F63" s="11">
         <v>95.52</v>
       </c>
-      <c r="G62" s="11">
+      <c r="G63" s="11">
         <v>536.08</v>
       </c>
-      <c r="H62" s="11">
+      <c r="H63" s="11">
         <v>170.8</v>
       </c>
-      <c r="I62" s="11">
+      <c r="I63" s="11">
         <v>415.02</v>
       </c>
-      <c r="J62" s="11">
+      <c r="J63" s="11">
         <v>121.06</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
-    <row r="64" s="1" customFormat="1" ht="65.5959" customHeight="1">
-      <c r="B64" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C64" s="13"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="13"/>
-      <c r="J64" s="13"/>
-      <c r="K64" s="13"/>
-    </row>
+    <row r="64" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
+    <row r="65" s="1" customFormat="1" ht="68.2624" customHeight="1">
+      <c r="B65" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="13"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13"/>
+      <c r="K65" s="13"/>
+    </row>
+    <row r="66" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B2:L2"/>
     <mergeCell ref="B4:B6"/>
-    <mergeCell ref="B64:K64"/>
+    <mergeCell ref="B65:K65"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="G4:J4"/>
